--- a/output/pdf_financials_xlsx/VRR.xlsx
+++ b/output/pdf_financials_xlsx/VRR.xlsx
@@ -4313,34 +4313,34 @@
         <v>0.05656</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.83662</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.929167</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.342496</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.715719</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.955666</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.407994</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.660596</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.903034</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.295854</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.997279</v>
       </c>
     </row>
     <row r="93">
@@ -5388,28 +5388,28 @@
         <v>-1.847144</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.06461</v>
+        <v>-1.760843</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.885907</v>
+        <v>-1.158524</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>-2.037028</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>1.712193</v>
+        <v>-0.7717079999999999</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>1.959236</v>
+        <v>-0.762999</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>6.330593</v>
+        <v>4.964874</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>2.426914</v>
+        <v>-0.343539</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.035472</v>
+        <v>-0.400359</v>
       </c>
     </row>
     <row r="119">
@@ -6907,7 +6907,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -7620,7 +7624,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -8306,7 +8314,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -8967,7 +8979,11 @@
           <t>Reserves (Note 8) 1,342,496</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -11703,7 +11719,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/VRR.xlsx
+++ b/output/pdf_financials_xlsx/VRR.xlsx
@@ -873,31 +873,31 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.015548</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.023075</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.011562</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.01854</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.007669</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.00447</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.003806</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.024312</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.007492</v>
       </c>
     </row>
     <row r="13">
@@ -1545,31 +1545,31 @@
         <v>-2.115436</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.965961</v>
+        <v>-0.981509</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.262965</v>
+        <v>-1.28604</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.596192</v>
+        <v>-1.607754</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.806926</v>
+        <v>-0.825466</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.61256</v>
+        <v>-2.620229</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-2.400945</v>
+        <v>-2.405415</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-7.085113</v>
+        <v>-7.088919</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-5.011613</v>
+        <v>-5.035925</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.9757479999999999</v>
+        <v>-0.98324</v>
       </c>
     </row>
     <row r="28">
@@ -1629,31 +1629,31 @@
         <v>-2.114926</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.964288</v>
+        <v>-0.979836</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.260728</v>
+        <v>-1.283803</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.594212</v>
+        <v>-1.605774</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.80554</v>
+        <v>-0.82408</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-2.61159</v>
+        <v>-2.619259</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-2.400266</v>
+        <v>-2.404736</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-7.084638</v>
+        <v>-7.088444</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-5.010503</v>
+        <v>-5.034815</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.9757479999999999</v>
+        <v>-0.98324</v>
       </c>
     </row>
     <row r="30">
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.325858</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>4.157167</v>
@@ -1857,16 +1857,16 @@
         <v>1.968469</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.744191</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>2.125958</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.246932</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>2.532086</v>
       </c>
     </row>
     <row r="35">
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.325858</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>4.157167</v>
@@ -1937,16 +1937,16 @@
         <v>1.968469</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.744191</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>2.125958</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.22918</v>
+        <v>0.476112</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>2.532086</v>
       </c>
     </row>
     <row r="37">
@@ -2396,7 +2396,7 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.325858</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.016</v>
@@ -2417,16 +2417,16 @@
         <v>0.06536400000000001</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.772529</v>
+        <v>0.028338</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.10979</v>
+        <v>2.983832</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.288005</v>
+        <v>0.041073</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.569488</v>
+        <v>1.037402</v>
       </c>
     </row>
     <row r="49">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -9417,7 +9417,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -19530,7 +19530,11 @@
           <t>Reclamation deposit</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -20763,7 +20767,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">

--- a/output/pdf_financials_xlsx/VRR.xlsx
+++ b/output/pdf_financials_xlsx/VRR.xlsx
@@ -1366,10 +1366,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-0.067221</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-2.115436</v>
@@ -3225,34 +3223,34 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.031787</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.027946</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.028238</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.022427</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.048267</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="68">
@@ -4578,10 +4576,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.067221</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-2.115436</v>
@@ -4620,10 +4616,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -4662,10 +4656,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.046882</v>
@@ -4704,10 +4696,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -4746,10 +4736,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>-0.01521</v>
@@ -4788,10 +4776,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.013865</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.253472</v>
@@ -4830,10 +4816,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -4872,10 +4856,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.013865</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.19138</v>
@@ -4914,10 +4896,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.0469</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>0.540959</v>
@@ -4956,10 +4936,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -4998,10 +4976,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -5040,10 +5016,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -5082,10 +5056,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -5124,10 +5096,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -5166,10 +5136,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -5208,10 +5176,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -5250,10 +5216,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -5283,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.914758</v>
       </c>
     </row>
     <row r="116">
@@ -5292,10 +5256,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -5334,10 +5296,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -5376,10 +5336,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>-0.308309</v>
@@ -5418,10 +5376,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.73225</v>
@@ -5460,10 +5416,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -5502,10 +5456,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -5544,10 +5496,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -5586,10 +5536,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -5628,10 +5576,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -5670,10 +5616,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -5712,10 +5656,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -5816,10 +5758,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>0</v>
@@ -5858,10 +5798,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.332314</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>5.04554</v>
@@ -5942,10 +5880,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0</v>
@@ -5984,10 +5920,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.325858</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>4.141755</v>
@@ -6068,10 +6002,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -6110,10 +6042,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.006456</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.171535</v>
@@ -6157,7 +6087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O250"/>
+  <dimension ref="A1:O319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11587,7 +11517,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
           <t>-</t>
@@ -19088,36 +19022,30 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B187" t="inlineStr"/>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>FOR THE YEARS ENDED MARCH</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F187" s="5" t="n">
-        <v>-2.115436</v>
-      </c>
-      <c r="G187" s="5" t="n">
-        <v>-0.965961</v>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H187" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="I187" t="inlineStr">
         <is>
@@ -19163,12 +19091,12 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Listing expense (Note 3)</t>
+          <t>Loss for the year $ (1,262,965) $</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
@@ -19177,18 +19105,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F188" s="5" t="n">
-        <v>1.184674</v>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H188" s="5" t="n">
+        <v>-0.965961</v>
       </c>
       <c r="I188" t="inlineStr">
         <is>
@@ -19234,17 +19162,17 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Net proceeds from the issuance of shares</t>
+          <t>Share-based payments 442,397</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -19252,16 +19180,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F189" s="5" t="n">
-        <v>5.04554</v>
-      </c>
-      <c r="G189" s="5" t="n">
-        <v>1.87946</v>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H189" s="5" t="n">
+        <v>0.116933</v>
       </c>
       <c r="I189" t="inlineStr">
         <is>
@@ -19307,17 +19237,17 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Depreciation 2,237</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -19325,16 +19255,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F190" s="5" t="n">
-        <v>5.04554</v>
-      </c>
-      <c r="G190" s="5" t="n">
-        <v>1.87946</v>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H190" s="5" t="n">
+        <v>0.001673</v>
       </c>
       <c r="I190" t="inlineStr">
         <is>
@@ -19380,12 +19312,12 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
+          <t>Impairment of exploration and evaluation assets 64,610</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -19398,16 +19330,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F191" s="5" t="n">
-        <v>-0.334688</v>
-      </c>
-      <c r="G191" s="5" t="n">
-        <v>-1.854738</v>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H191" s="5" t="n">
+        <v>0.007594</v>
       </c>
       <c r="I191" t="inlineStr">
         <is>
@@ -19453,12 +19387,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Equipment</t>
+          <t>Receivables (1,342)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -19467,16 +19401,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F192" s="5" t="n">
-        <v>-0.003913</v>
-      </c>
-      <c r="G192" s="5" t="n">
-        <v>-0.004344</v>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H192" s="5" t="n">
+        <v>0.031831</v>
       </c>
       <c r="I192" t="inlineStr">
         <is>
@@ -19522,36 +19458,32 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Reclamation deposit</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr">
-        <is>
-          <t>ChangeInRestrictedCash</t>
-        </is>
-      </c>
+          <t>Prepaid expenses (483)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F193" s="5" t="n">
-        <v>0.021279</v>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H193" s="5" t="n">
+        <v>0.004269</v>
       </c>
       <c r="I193" t="inlineStr">
         <is>
@@ -19597,32 +19529,36 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Transaction costs (Note 3)</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 5,286</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F194" s="5" t="n">
-        <v>-0.537819</v>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H194" s="5" t="n">
+        <v>-0.287951</v>
       </c>
       <c r="I194" t="inlineStr">
         <is>
@@ -19668,32 +19604,36 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Cash acquired from reverse acquisition (Note 3)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Net cash used in operating activities (750,260)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F195" s="5" t="n">
-        <v>0.122891</v>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H195" s="5" t="n">
+        <v>-1.091612</v>
       </c>
       <c r="I195" t="inlineStr">
         <is>
@@ -19739,17 +19679,17 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Net proceeds from the issuance of shares 733,278</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -19757,16 +19697,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F196" s="5" t="n">
-        <v>-0.73225</v>
-      </c>
-      <c r="G196" s="5" t="n">
-        <v>-1.859082</v>
-      </c>
-      <c r="H196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H196" s="5" t="n">
+        <v>1.87946</v>
       </c>
       <c r="I196" t="inlineStr">
         <is>
@@ -19812,30 +19754,36 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Change in cash and cash equivalents during the year</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
+          <t>Net cash provided by financing activities 733,278</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F197" s="5" t="n">
-        <v>4.141755</v>
-      </c>
-      <c r="G197" s="5" t="n">
-        <v>-1.071234</v>
-      </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H197" s="5" t="n">
+        <v>1.87946</v>
       </c>
       <c r="I197" t="inlineStr">
         <is>
@@ -19886,29 +19834,27 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, beginning of year</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenditures (1,825,453)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F198" s="5" t="n">
-        <v>0.015412</v>
-      </c>
-      <c r="G198" s="5" t="n">
-        <v>4.157167</v>
-      </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H198" s="5" t="n">
+        <v>-1.854738</v>
       </c>
       <c r="I198" t="inlineStr">
         <is>
@@ -19959,29 +19905,27 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents, end of year $</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Equipment (2,763)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F199" s="5" t="n">
-        <v>4.157167</v>
-      </c>
-      <c r="G199" s="5" t="n">
-        <v>3.085933</v>
-      </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H199" s="5" t="n">
+        <v>-0.004344</v>
       </c>
       <c r="I199" t="inlineStr">
         <is>
@@ -20027,12 +19971,12 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Cash paid during the year for</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>710,186          945,000 (15,750)  4,000,000 414,709  (127,783)  (280,000) - 315,000 630,000 540,959 80,932 13,139                         5,110,956            2,007,500 (29,176) 31,000 (20,500) 181,000 116,933 - (12,750)  (965,961)            6,419,002                     Total                                                                                                                                                                                                     (2,115,436)</t>
+          <t>Net cash used in investing activities (1,828,216)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr"/>
@@ -20041,18 +19985,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F200" s="5" t="n">
-        <v>0.312936</v>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H200" s="5" t="n">
+        <v>-1.859082</v>
       </c>
       <c r="I200" t="inlineStr">
         <is>
@@ -20093,83 +20037,93 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 11) $</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents during the year (1,845,198)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F201" s="5" t="n">
-        <v>0.09532400000000001</v>
-      </c>
-      <c r="G201" s="5" t="n">
-        <v>0.06378</v>
-      </c>
-      <c r="H201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H201" s="5" t="n">
+        <v>-1.071234</v>
       </c>
       <c r="I201" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J201" s="5" t="n">
-        <v>0.0485</v>
-      </c>
-      <c r="K201" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L201" s="5" t="n">
-        <v>0.031263</v>
-      </c>
-      <c r="M201" s="5" t="n">
-        <v>0.07373</v>
-      </c>
-      <c r="N201" s="5" t="n">
-        <v>0.073628</v>
-      </c>
-      <c r="O201" s="5" t="n">
-        <v>0.063858</v>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Cash and cash equivalents, beginning of year 3,085,933</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -20187,10 +20141,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H202" s="5" t="n">
+        <v>4.157167</v>
       </c>
       <c r="I202" t="inlineStr">
         <is>
@@ -20217,8 +20169,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N202" s="5" t="n">
-        <v>0.00111</v>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -20229,22 +20183,22 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Cash and cash equivalents, end of year $ 1,240,735 $</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -20262,49 +20216,59 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H203" s="5" t="n">
+        <v>3.085933</v>
       </c>
       <c r="I203" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J203" s="5" t="n">
-        <v>0.038346</v>
-      </c>
-      <c r="K203" s="5" t="n">
-        <v>0.012552</v>
-      </c>
-      <c r="L203" s="5" t="n">
-        <v>-0.006385</v>
-      </c>
-      <c r="M203" s="5" t="n">
-        <v>0.01737</v>
-      </c>
-      <c r="N203" s="5" t="n">
-        <v>0.020961</v>
-      </c>
-      <c r="O203" s="5" t="n">
-        <v>0.006168</v>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash paid during the year for</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Investor relations and promotion</t>
+          <t>Income taxes $ - $</t>
         </is>
       </c>
       <c r="D204" t="inlineStr"/>
@@ -20313,222 +20277,286 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F204" s="5" t="n">
-        <v>0.009155</v>
-      </c>
-      <c r="G204" s="5" t="n">
-        <v>0.140517</v>
-      </c>
-      <c r="H204" s="5" t="n">
-        <v>0.187218</v>
-      </c>
-      <c r="I204" s="5" t="n">
-        <v>0.123935</v>
-      </c>
-      <c r="J204" s="5" t="n">
-        <v>0.054299</v>
-      </c>
-      <c r="K204" s="5" t="n">
-        <v>0.119414</v>
-      </c>
-      <c r="L204" s="5" t="n">
-        <v>0.185902</v>
-      </c>
-      <c r="M204" s="5" t="n">
-        <v>0.071007</v>
-      </c>
-      <c r="N204" s="5" t="n">
-        <v>0.179306</v>
-      </c>
-      <c r="O204" s="5" t="n">
-        <v>0.349885</v>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash paid during the year for</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Office</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Interest $ - $</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F205" s="5" t="n">
-        <v>0.016538</v>
-      </c>
-      <c r="G205" s="5" t="n">
-        <v>0.032497</v>
-      </c>
-      <c r="H205" s="5" t="n">
-        <v>0.045087</v>
-      </c>
-      <c r="I205" s="5" t="n">
-        <v>0.036457</v>
-      </c>
-      <c r="J205" s="5" t="n">
-        <v>0.051405</v>
-      </c>
-      <c r="K205" s="5" t="n">
-        <v>0.058231</v>
-      </c>
-      <c r="L205" s="5" t="n">
-        <v>0.08856</v>
-      </c>
-      <c r="M205" s="5" t="n">
-        <v>0.076284</v>
-      </c>
-      <c r="N205" s="5" t="n">
-        <v>0.07979</v>
-      </c>
-      <c r="O205" s="5" t="n">
-        <v>0.055198</v>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash paid during the year for</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Supplemental disclosure with respect to cash flows (Note</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F206" s="5" t="n">
-        <v>0.07206799999999999</v>
-      </c>
-      <c r="G206" s="5" t="n">
-        <v>0.09639499999999999</v>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H206" s="5" t="n">
-        <v>0.070399</v>
-      </c>
-      <c r="I206" s="5" t="n">
-        <v>0.0558</v>
-      </c>
-      <c r="J206" s="5" t="n">
-        <v>0.061806</v>
-      </c>
-      <c r="K206" s="5" t="n">
-        <v>0.041066</v>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v>0.106525</v>
-      </c>
-      <c r="M206" s="5" t="n">
-        <v>0.094221</v>
-      </c>
-      <c r="N206" s="5" t="n">
-        <v>0.131447</v>
-      </c>
-      <c r="O206" s="5" t="n">
-        <v>0.262593</v>
+        <v>9e-06</v>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Rent</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance as at March 31, 2017 35,405,225 $ 8,485,349 $ 836,620 $ (4,536,699) $ 325,686 $</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F207" s="5" t="n">
-        <v>0.012333</v>
-      </c>
-      <c r="G207" s="5" t="n">
-        <v>0.024122</v>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H207" s="5" t="n">
-        <v>0.043327</v>
-      </c>
-      <c r="I207" s="5" t="n">
-        <v>0.045167</v>
-      </c>
-      <c r="J207" s="5" t="n">
-        <v>0.02077</v>
-      </c>
-      <c r="K207" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L207" s="5" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="M207" s="5" t="n">
-        <v>0.021425</v>
-      </c>
-      <c r="N207" s="5" t="n">
-        <v>0.0194</v>
-      </c>
-      <c r="O207" s="5" t="n">
-        <v>0.01545</v>
+        <v>5.110956</v>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Salaries (Note 11)</t>
+          <t>Private placement 8,030,000 2,007,500 - - -</t>
         </is>
       </c>
       <c r="D208" t="inlineStr"/>
@@ -20537,55 +20565,69 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F208" s="5" t="n">
-        <v>0.104625</v>
-      </c>
-      <c r="G208" s="5" t="n">
-        <v>0.382843</v>
-      </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H208" s="5" t="n">
+        <v>2.0075</v>
       </c>
       <c r="I208" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J208" s="5" t="n">
-        <v>0.269814</v>
-      </c>
-      <c r="K208" s="5" t="n">
-        <v>0.277932</v>
-      </c>
-      <c r="L208" s="5" t="n">
-        <v>0.256712</v>
-      </c>
-      <c r="M208" s="5" t="n">
-        <v>0.287225</v>
-      </c>
-      <c r="N208" s="5" t="n">
-        <v>0.326578</v>
-      </c>
-      <c r="O208" s="5" t="n">
-        <v>0.23893</v>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 9 and 11)</t>
+          <t>Share issue cost - Private placement 1,262,965 (29,176) - - -</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -20604,10 +20646,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H209" s="5" t="n">
+        <v>-0.029176</v>
       </c>
       <c r="I209" t="inlineStr">
         <is>
@@ -20619,157 +20659,191 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K209" s="5" t="n">
-        <v>0.426574</v>
-      </c>
-      <c r="L209" s="5" t="n">
-        <v>0.136211</v>
-      </c>
-      <c r="M209" s="5" t="n">
-        <v>0.242438</v>
-      </c>
-      <c r="N209" s="5" t="n">
-        <v>0.288381</v>
-      </c>
-      <c r="O209" s="5" t="n">
-        <v>0.479571</v>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Options exercised 300,000 31,000 - - -</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F210" s="5" t="n">
-        <v>0.012823</v>
-      </c>
-      <c r="G210" s="5" t="n">
-        <v>0.062809</v>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H210" s="5" t="n">
-        <v>0.027725</v>
-      </c>
-      <c r="I210" s="5" t="n">
-        <v>0.033272</v>
-      </c>
-      <c r="J210" s="5" t="n">
-        <v>0.049986</v>
-      </c>
-      <c r="K210" s="5" t="n">
-        <v>0.046619</v>
-      </c>
-      <c r="L210" s="5" t="n">
-        <v>0.04147</v>
-      </c>
-      <c r="M210" s="5" t="n">
-        <v>0.048799</v>
-      </c>
-      <c r="N210" s="5" t="n">
-        <v>0.056658</v>
-      </c>
-      <c r="O210" s="5" t="n">
-        <v>0.051745</v>
+        <v>0.031</v>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Finders' fee - cash - (20,500) - - -</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F211" s="5" t="n">
-        <v>0.930762</v>
-      </c>
-      <c r="G211" s="5" t="n">
-        <v>0.981509</v>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H211" s="5" t="n">
-        <v>1.28604</v>
-      </c>
-      <c r="I211" s="5" t="n">
-        <v>1.827754</v>
-      </c>
-      <c r="J211" s="5" t="n">
-        <v>0.813373</v>
-      </c>
-      <c r="K211" s="5" t="n">
-        <v>1.031358</v>
-      </c>
-      <c r="L211" s="5" t="n">
-        <v>0.864937</v>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v>0.932974</v>
-      </c>
-      <c r="N211" s="5" t="n">
-        <v>1.177259</v>
-      </c>
-      <c r="O211" s="5" t="n">
-        <v>1.523398</v>
+        <v>-0.0205</v>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Property acquisition 550,000 181,000 - - -</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -20780,48 +20854,64 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G212" s="5" t="n">
-        <v>0.015548</v>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H212" s="5" t="n">
-        <v>0.023075</v>
-      </c>
-      <c r="I212" s="5" t="n">
-        <v>0.011562</v>
-      </c>
-      <c r="J212" s="5" t="n">
-        <v>0.01854</v>
-      </c>
-      <c r="K212" s="5" t="n">
-        <v>0.007669</v>
-      </c>
-      <c r="L212" s="5" t="n">
-        <v>0.00447</v>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v>0.003806</v>
-      </c>
-      <c r="N212" s="5" t="n">
-        <v>0.024312</v>
-      </c>
-      <c r="O212" s="5" t="n">
-        <v>0.007492</v>
+        <v>0.181</v>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Other income – flow-through</t>
+          <t>Share-based payments - - 116,933 - -</t>
         </is>
       </c>
       <c r="D213" t="inlineStr"/>
@@ -20840,10 +20930,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H213" s="5" t="n">
+        <v>0.116933</v>
       </c>
       <c r="I213" t="inlineStr">
         <is>
@@ -20870,8 +20958,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N213" s="5" t="n">
-        <v>0.015546</v>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -20882,17 +20972,17 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 6)</t>
+          <t>Recalssification of reserves on exercise of options - 24,386 (24,386) - -</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -20921,39 +21011,51 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J214" s="5" t="n">
-        <v>-0.012093</v>
-      </c>
-      <c r="K214" s="5" t="n">
-        <v>-1.712193</v>
-      </c>
-      <c r="L214" s="5" t="n">
-        <v>-1.959236</v>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v>-6.330593</v>
-      </c>
-      <c r="N214" s="5" t="n">
-        <v>-2.426914</v>
-      </c>
-      <c r="O214" s="5" t="n">
-        <v>-0.035472</v>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Impairment of asset held for sale (Note 3)</t>
+          <t>Translation adjustment - - - - (12,750)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr"/>
@@ -20972,10 +21074,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H215" s="5" t="n">
+        <v>-0.01275</v>
       </c>
       <c r="I215" t="inlineStr">
         <is>
@@ -21002,8 +21102,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N215" s="5" t="n">
-        <v>-1.56947</v>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O215" t="inlineStr">
         <is>
@@ -21014,17 +21116,17 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Part XII.6 flow through tax</t>
+          <t>Loss for the year - - - (965,961) -</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -21043,10 +21145,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H216" s="5" t="n">
+        <v>-0.965961</v>
       </c>
       <c r="I216" t="inlineStr">
         <is>
@@ -21073,8 +21173,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N216" s="5" t="n">
-        <v>-0.006426</v>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O216" t="inlineStr">
         <is>
@@ -21085,17 +21187,17 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Proceeds on sale of resource property (Note 6(c))</t>
+          <t>Balance as at March 31, 2018 45,548,190 $ 10,679,559 $ 929,167 $ (5,502,660) $ 312,936 $</t>
         </is>
       </c>
       <c r="D217" t="inlineStr"/>
@@ -21114,10 +21216,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H217" s="5" t="n">
+        <v>6.419002</v>
       </c>
       <c r="I217" t="inlineStr">
         <is>
@@ -21144,8 +21244,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N217" s="5" t="n">
-        <v>0.1</v>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O217" t="inlineStr">
         <is>
@@ -21156,17 +21258,17 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Realized gain on marketable securities (Note 4)</t>
+          <t>Private placement 2,595,925 700,900 - - -</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
@@ -21185,10 +21287,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H218" s="5" t="n">
+        <v>0.7009</v>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -21220,24 +21320,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O218" s="5" t="n">
-        <v>0.57563</v>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Unrealized gain on marketable securities (Note 4)</t>
+          <t>Share issue cost - Private placement (30,455) - - -</t>
         </is>
       </c>
       <c r="D219" t="inlineStr"/>
@@ -21256,10 +21358,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H219" s="5" t="n">
+        <v>-0.030455</v>
       </c>
       <c r="I219" t="inlineStr">
         <is>
@@ -21286,8 +21386,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N219" s="5" t="n">
-        <v>0.028598</v>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O219" t="inlineStr">
         <is>
@@ -21298,74 +21400,88 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Options exercised 250,000 44,500 - - -</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F220" s="5" t="n">
-        <v>-2.115436</v>
-      </c>
-      <c r="G220" s="5" t="n">
-        <v>-0.965961</v>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H220" s="5" t="n">
-        <v>-1.262965</v>
-      </c>
-      <c r="I220" s="5" t="n">
-        <v>-1.596192</v>
-      </c>
-      <c r="J220" s="5" t="n">
-        <v>-0.806926</v>
-      </c>
-      <c r="K220" s="5" t="n">
-        <v>-2.61256</v>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v>-2.400945</v>
-      </c>
-      <c r="M220" s="5" t="n">
-        <v>-7.085113</v>
-      </c>
-      <c r="N220" s="5" t="n">
-        <v>-5.011613</v>
-      </c>
-      <c r="O220" s="5" t="n">
-        <v>-0.9757479999999999</v>
+        <v>0.0445</v>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Translation adjustment</t>
+          <t>Warrants exercised 61,110 18,333 - - -</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -21384,56 +21500,62 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H221" s="5" t="n">
+        <v>0.018333</v>
       </c>
       <c r="I221" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J221" s="5" t="n">
-        <v>-0.511493</v>
-      </c>
-      <c r="K221" s="5" t="n">
-        <v>-0.032515</v>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v>0.5016389999999999</v>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v>0.022187</v>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v>0.14693</v>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v>-0.05701</v>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property acquisition 200,000 55,000 - - -</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -21449,106 +21571,130 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H222" s="5" t="n">
+        <v>0.055</v>
       </c>
       <c r="I222" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J222" s="5" t="n">
-        <v>-1.318419</v>
-      </c>
-      <c r="K222" s="5" t="n">
-        <v>-2.645075</v>
-      </c>
-      <c r="L222" s="5" t="n">
-        <v>-1.899306</v>
-      </c>
-      <c r="M222" s="5" t="n">
-        <v>-7.062926</v>
-      </c>
-      <c r="N222" s="5" t="n">
-        <v>-4.864683</v>
-      </c>
-      <c r="O222" s="5" t="n">
-        <v>-1.032758</v>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Loss per common share</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>-Basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share-based payments - - 442,397 - -</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F223" s="5" t="n">
-        <v>-1.3e-07</v>
-      </c>
-      <c r="G223" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H223" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="I223" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J223" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="K223" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="M223" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
-      </c>
-      <c r="N223" s="5" t="n">
-        <v>-4e-07</v>
-      </c>
-      <c r="O223" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.442397</v>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Weighted average number of common shares outstanding</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>-Basic and diluted</t>
+          <t>Recalssification of reserves on exercise of options - 29,068 (29,068) - -</t>
         </is>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -21557,58 +21703,74 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F224" s="5" t="n">
-        <v>16.737212</v>
-      </c>
-      <c r="G224" s="5" t="n">
-        <v>36.092157</v>
-      </c>
-      <c r="H224" s="5" t="n">
-        <v>47.155675</v>
-      </c>
-      <c r="I224" s="5" t="n">
-        <v>55.859491</v>
-      </c>
-      <c r="J224" s="5" t="n">
-        <v>70.309409</v>
-      </c>
-      <c r="K224" s="5" t="n">
-        <v>81.126475</v>
-      </c>
-      <c r="L224" s="5" t="n">
-        <v>91.04077599999999</v>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v>112.559691</v>
-      </c>
-      <c r="N224" s="5" t="n">
-        <v>12.396226</v>
-      </c>
-      <c r="O224" s="5" t="n">
-        <v>17.486256</v>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 12) $</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Translation adjustment - - - - 123,584</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
@@ -21624,10 +21786,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H225" s="5" t="n">
+        <v>0.123584</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -21649,11 +21809,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M225" s="5" t="n">
-        <v>0.07373</v>
-      </c>
-      <c r="N225" s="5" t="n">
-        <v>0.073628</v>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -21664,39 +21828,37 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Depreciation (Note 6)</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Loss for the year - - - (1,262,965) -</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F226" s="5" t="n">
-        <v>0.00051</v>
-      </c>
-      <c r="G226" s="5" t="n">
-        <v>0.001673</v>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-1.262965</v>
       </c>
       <c r="I226" t="inlineStr">
         <is>
@@ -21718,11 +21880,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M226" s="5" t="n">
-        <v>0.000475</v>
-      </c>
-      <c r="N226" s="5" t="n">
-        <v>0.00111</v>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O226" t="inlineStr">
         <is>
@@ -21733,17 +21899,17 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Shares          Amount          Reserves              Deficit           Income             Total</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Salaries (Note 12)</t>
+          <t>Balance as at March 31, 2019 48,655,225 $ 11,496,905 $ 1,342,496 $ (6,765,625) $ 436,520 $</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -21762,10 +21928,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H227" s="5" t="n">
+        <v>6.510296</v>
       </c>
       <c r="I227" t="inlineStr">
         <is>
@@ -21787,11 +21951,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M227" s="5" t="n">
-        <v>0.287225</v>
-      </c>
-      <c r="N227" s="5" t="n">
-        <v>0.326578</v>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O227" t="inlineStr">
         <is>
@@ -21802,34 +21970,34 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 10 and 12)</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F228" s="5" t="n">
+        <v>-2.115436</v>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>-0.965961</v>
       </c>
       <c r="H228" t="inlineStr">
         <is>
@@ -21856,11 +22024,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M228" s="5" t="n">
-        <v>0.242438</v>
-      </c>
-      <c r="N228" s="5" t="n">
-        <v>0.288381</v>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -21871,17 +22043,17 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Other income – flow-through (Note 10)</t>
+          <t>Listing expense (Note 3)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr"/>
@@ -21890,10 +22062,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F229" s="5" t="n">
+        <v>1.184674</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -21925,11 +22095,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M229" s="5" t="n">
-        <v>0.174648</v>
-      </c>
-      <c r="N229" s="5" t="n">
-        <v>0.015546</v>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O229" t="inlineStr">
         <is>
@@ -21940,34 +22114,34 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 7)</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
+          <t>Net proceeds from the issuance of shares</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F230" s="5" t="n">
+        <v>5.04554</v>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>1.87946</v>
       </c>
       <c r="H230" t="inlineStr">
         <is>
@@ -21994,11 +22168,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M230" s="5" t="n">
-        <v>-6.330593</v>
-      </c>
-      <c r="N230" s="5" t="n">
-        <v>-2.426914</v>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O230" t="inlineStr">
         <is>
@@ -22009,34 +22187,34 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Impairment of asset held for sale (Note 4)</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F231" s="5" t="n">
+        <v>5.04554</v>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>1.87946</v>
       </c>
       <c r="H231" t="inlineStr">
         <is>
@@ -22068,8 +22246,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N231" s="5" t="n">
-        <v>-1.56947</v>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O231" t="inlineStr">
         <is>
@@ -22080,34 +22260,34 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Proceeds on sale of resource property (Note 7(d))</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F232" s="5" t="n">
+        <v>-0.334688</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>-1.854738</v>
       </c>
       <c r="H232" t="inlineStr">
         <is>
@@ -22139,8 +22319,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N232" s="5" t="n">
-        <v>0.1</v>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O232" t="inlineStr">
         <is>
@@ -22151,56 +22333,60 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Depreciation (Note 5)</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Equipment</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G233" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H233" s="5" t="n">
-        <v>0.002237</v>
-      </c>
-      <c r="I233" s="5" t="n">
-        <v>0.00198</v>
-      </c>
-      <c r="J233" s="5" t="n">
-        <v>0.001386</v>
-      </c>
-      <c r="K233" s="5" t="n">
-        <v>0.0009700000000000001</v>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v>0.000679</v>
-      </c>
-      <c r="M233" s="5" t="n">
-        <v>0.000475</v>
+      <c r="F233" s="5" t="n">
+        <v>-0.003913</v>
+      </c>
+      <c r="G233" s="5" t="n">
+        <v>-0.004344</v>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N233" t="inlineStr">
         <is>
@@ -22216,29 +22402,31 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Other income – flow-through (Note 9)</t>
-        </is>
-      </c>
-      <c r="D234" t="inlineStr"/>
+          <t>Reclamation deposit</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E234" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F234" s="5" t="n">
+        <v>0.021279</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -22260,14 +22448,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K234" s="5" t="n">
-        <v>0.123322</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>0.418758</v>
-      </c>
-      <c r="M234" s="5" t="n">
-        <v>0.174648</v>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N234" t="inlineStr">
         <is>
@@ -22283,17 +22477,17 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 9(b) and 11)</t>
+          <t>Transaction costs (Note 3)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
@@ -22302,10 +22496,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F235" s="5" t="n">
+        <v>-0.537819</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -22322,11 +22514,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J235" s="5" t="n">
-        <v>0.216867</v>
-      </c>
-      <c r="K235" s="5" t="n">
-        <v>0.426574</v>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
@@ -22352,43 +22548,47 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Cash acquired from reverse acquisition (Note 3)</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F236" s="5" t="n">
-        <v>0.019341</v>
-      </c>
-      <c r="G236" s="5" t="n">
-        <v>0.01599</v>
-      </c>
-      <c r="H236" s="5" t="n">
-        <v>0.022424</v>
-      </c>
-      <c r="I236" s="5" t="n">
-        <v>0.015328</v>
-      </c>
-      <c r="J236" s="5" t="n">
-        <v>0.000194</v>
+        <v>0.122891</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
@@ -22419,34 +22619,34 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Other income – flow-through (Note 9(a))</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G237" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F237" s="5" t="n">
+        <v>-0.73225</v>
+      </c>
+      <c r="G237" s="5" t="n">
+        <v>-1.859082</v>
       </c>
       <c r="H237" t="inlineStr">
         <is>
@@ -22463,8 +22663,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K237" s="5" t="n">
-        <v>0.123322</v>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
@@ -22490,44 +22692,40 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Consulting fees (Note 10) $</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Change in cash and cash equivalents during the year</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G238" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H238" s="5" t="n">
-        <v>0.08519699999999999</v>
-      </c>
-      <c r="I238" s="5" t="n">
-        <v>0.069815</v>
+      <c r="F238" s="5" t="n">
+        <v>4.141755</v>
+      </c>
+      <c r="G238" s="5" t="n">
+        <v>-1.071234</v>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J238" t="inlineStr">
         <is>
@@ -22563,22 +22761,22 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
+          <t>Cash and cash equivalents, beginning of year</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -22586,21 +22784,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G239" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H239" s="5" t="n">
-        <v>-0.08019</v>
-      </c>
-      <c r="I239" s="5" t="n">
-        <v>-0.031979</v>
+      <c r="F239" s="5" t="n">
+        <v>0.015412</v>
+      </c>
+      <c r="G239" s="5" t="n">
+        <v>4.157167</v>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J239" t="inlineStr">
         <is>
@@ -22636,40 +22834,44 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 6)</t>
-        </is>
-      </c>
-      <c r="D240" t="inlineStr"/>
+          <t>Cash and cash equivalents, end of year $</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H240" s="5" t="n">
-        <v>0.06461</v>
-      </c>
-      <c r="I240" s="5" t="n">
-        <v>0.885907</v>
+      <c r="F240" s="5" t="n">
+        <v>4.157167</v>
+      </c>
+      <c r="G240" s="5" t="n">
+        <v>3.085933</v>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J240" t="inlineStr">
         <is>
@@ -22705,17 +22907,17 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Cash paid during the year for</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Salaries (Note 10)</t>
+          <t>710,186          945,000 (15,750)  4,000,000 414,709  (127,783)  (280,000) - 315,000 630,000 540,959 80,932 13,139                         5,110,956            2,007,500 (29,176) 31,000 (20,500) 181,000 116,933 - (12,750)  (965,961)            6,419,002                     Total                                                                                                                                                                                                     (2,115,436)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr"/>
@@ -22724,21 +22926,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F241" s="5" t="n">
+        <v>0.312936</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H241" s="5" t="n">
-        <v>0.375609</v>
-      </c>
-      <c r="I241" s="5" t="n">
-        <v>0.239886</v>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
@@ -22774,24 +22978,26 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 8(b) and 10)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="n">
+        <v>-0.067221</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22803,11 +23009,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H242" s="5" t="n">
-        <v>0.442397</v>
-      </c>
-      <c r="I242" s="5" t="n">
-        <v>0.352186</v>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
@@ -22843,24 +23053,26 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>OTHER</t>
+          <t>Add back items not involving cash</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Other income – flow-through (Note 8(a))</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="n">
+        <v>0.013865</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22877,8 +23089,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I243" s="5" t="n">
-        <v>0.22</v>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
@@ -22914,36 +23128,46 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>Add back items not involving cash</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Translation adjustment</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr"/>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F244" s="5" t="n">
-        <v>0.013139</v>
-      </c>
-      <c r="G244" s="5" t="n">
-        <v>-0.01275</v>
-      </c>
-      <c r="H244" s="5" t="n">
-        <v>0.123584</v>
-      </c>
-      <c r="I244" s="5" t="n">
-        <v>0.247218</v>
+          <t>Share-based compensation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="n">
+        <v>0.0469</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
@@ -22979,40 +23203,46 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>years</t>
+          <t>Add back items not involving cash</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss for the year $</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F245" s="5" t="n">
-        <v>-2.102297</v>
-      </c>
-      <c r="G245" s="5" t="n">
-        <v>-0.978711</v>
-      </c>
-      <c r="H245" s="5" t="n">
-        <v>-1.139381</v>
-      </c>
-      <c r="I245" s="5" t="n">
-        <v>-1.348974</v>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="n">
+        <v>-0.006456</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
@@ -23048,34 +23278,32 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F246" s="5" t="n">
-        <v>0.015308</v>
-      </c>
-      <c r="G246" s="5" t="n">
-        <v>0.036356</v>
+          <t>Issuance of common shares, net of costs (Note 6)</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" s="5" t="n">
+        <v>0.332314</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
@@ -23121,30 +23349,36 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 7(a))</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F247" s="5" t="n">
-        <v>0.026379</v>
-      </c>
-      <c r="G247" s="5" t="n">
-        <v>0.007594</v>
+          <t>Cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="n">
+        <v>0.332314</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
@@ -23190,27 +23424,27 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>Increase in cash resources</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F248" s="5" t="n">
-        <v>0.005399</v>
+      <c r="E248" s="5" t="n">
+        <v>0.325858</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -23261,17 +23495,17 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 9(b))</t>
+          <t>Cash resources, beginning of period</t>
         </is>
       </c>
       <c r="D249" t="inlineStr"/>
@@ -23280,11 +23514,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F249" s="5" t="n">
-        <v>0.540959</v>
-      </c>
-      <c r="G249" s="5" t="n">
-        <v>0.116933</v>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
@@ -23330,69 +23568,4754 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Cash resources, end of period $</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" s="5" t="n">
+        <v>0.325858</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B250" t="inlineStr">
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 11) $</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F251" s="5" t="n">
+        <v>0.09532400000000001</v>
+      </c>
+      <c r="G251" s="5" t="n">
+        <v>0.06378</v>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J251" s="5" t="n">
+        <v>0.0485</v>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>0.031263</v>
+      </c>
+      <c r="M251" s="5" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="N251" s="5" t="n">
+        <v>0.073628</v>
+      </c>
+      <c r="O251" s="5" t="n">
+        <v>0.063858</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="5" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J253" s="5" t="n">
+        <v>0.038346</v>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>0.012552</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>-0.006385</v>
+      </c>
+      <c r="M253" s="5" t="n">
+        <v>0.01737</v>
+      </c>
+      <c r="N253" s="5" t="n">
+        <v>0.020961</v>
+      </c>
+      <c r="O253" s="5" t="n">
+        <v>0.006168</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Investor relations and promotion</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F254" s="5" t="n">
+        <v>0.009155</v>
+      </c>
+      <c r="G254" s="5" t="n">
+        <v>0.140517</v>
+      </c>
+      <c r="H254" s="5" t="n">
+        <v>0.187218</v>
+      </c>
+      <c r="I254" s="5" t="n">
+        <v>0.123935</v>
+      </c>
+      <c r="J254" s="5" t="n">
+        <v>0.054299</v>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>0.119414</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>0.185902</v>
+      </c>
+      <c r="M254" s="5" t="n">
+        <v>0.071007</v>
+      </c>
+      <c r="N254" s="5" t="n">
+        <v>0.179306</v>
+      </c>
+      <c r="O254" s="5" t="n">
+        <v>0.349885</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F255" s="5" t="n">
+        <v>0.016538</v>
+      </c>
+      <c r="G255" s="5" t="n">
+        <v>0.032497</v>
+      </c>
+      <c r="H255" s="5" t="n">
+        <v>0.045087</v>
+      </c>
+      <c r="I255" s="5" t="n">
+        <v>0.036457</v>
+      </c>
+      <c r="J255" s="5" t="n">
+        <v>0.051405</v>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>0.058231</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>0.08856</v>
+      </c>
+      <c r="M255" s="5" t="n">
+        <v>0.076284</v>
+      </c>
+      <c r="N255" s="5" t="n">
+        <v>0.07979</v>
+      </c>
+      <c r="O255" s="5" t="n">
+        <v>0.055198</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F256" s="5" t="n">
+        <v>0.07206799999999999</v>
+      </c>
+      <c r="G256" s="5" t="n">
+        <v>0.09639499999999999</v>
+      </c>
+      <c r="H256" s="5" t="n">
+        <v>0.070399</v>
+      </c>
+      <c r="I256" s="5" t="n">
+        <v>0.0558</v>
+      </c>
+      <c r="J256" s="5" t="n">
+        <v>0.061806</v>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>0.041066</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>0.106525</v>
+      </c>
+      <c r="M256" s="5" t="n">
+        <v>0.094221</v>
+      </c>
+      <c r="N256" s="5" t="n">
+        <v>0.131447</v>
+      </c>
+      <c r="O256" s="5" t="n">
+        <v>0.262593</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Rent</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F257" s="5" t="n">
+        <v>0.012333</v>
+      </c>
+      <c r="G257" s="5" t="n">
+        <v>0.024122</v>
+      </c>
+      <c r="H257" s="5" t="n">
+        <v>0.043327</v>
+      </c>
+      <c r="I257" s="5" t="n">
+        <v>0.045167</v>
+      </c>
+      <c r="J257" s="5" t="n">
+        <v>0.02077</v>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="M257" s="5" t="n">
+        <v>0.021425</v>
+      </c>
+      <c r="N257" s="5" t="n">
+        <v>0.0194</v>
+      </c>
+      <c r="O257" s="5" t="n">
+        <v>0.01545</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Salaries (Note 11)</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F258" s="5" t="n">
+        <v>0.104625</v>
+      </c>
+      <c r="G258" s="5" t="n">
+        <v>0.382843</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J258" s="5" t="n">
+        <v>0.269814</v>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>0.277932</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>0.256712</v>
+      </c>
+      <c r="M258" s="5" t="n">
+        <v>0.287225</v>
+      </c>
+      <c r="N258" s="5" t="n">
+        <v>0.326578</v>
+      </c>
+      <c r="O258" s="5" t="n">
+        <v>0.23893</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 9 and 11)</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>0.426574</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>0.136211</v>
+      </c>
+      <c r="M259" s="5" t="n">
+        <v>0.242438</v>
+      </c>
+      <c r="N259" s="5" t="n">
+        <v>0.288381</v>
+      </c>
+      <c r="O259" s="5" t="n">
+        <v>0.479571</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Regulatory and transfer agent</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="n">
+        <v>0.012823</v>
+      </c>
+      <c r="G260" s="5" t="n">
+        <v>0.062809</v>
+      </c>
+      <c r="H260" s="5" t="n">
+        <v>0.027725</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>0.033272</v>
+      </c>
+      <c r="J260" s="5" t="n">
+        <v>0.049986</v>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>0.046619</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>0.04147</v>
+      </c>
+      <c r="M260" s="5" t="n">
+        <v>0.048799</v>
+      </c>
+      <c r="N260" s="5" t="n">
+        <v>0.056658</v>
+      </c>
+      <c r="O260" s="5" t="n">
+        <v>0.051745</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F261" s="5" t="n">
+        <v>0.930762</v>
+      </c>
+      <c r="G261" s="5" t="n">
+        <v>0.981509</v>
+      </c>
+      <c r="H261" s="5" t="n">
+        <v>1.28604</v>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>1.827754</v>
+      </c>
+      <c r="J261" s="5" t="n">
+        <v>0.813373</v>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>1.031358</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>0.864937</v>
+      </c>
+      <c r="M261" s="5" t="n">
+        <v>0.932974</v>
+      </c>
+      <c r="N261" s="5" t="n">
+        <v>1.177259</v>
+      </c>
+      <c r="O261" s="5" t="n">
+        <v>1.523398</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
         <is>
           <t>OTHER</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr">
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G262" s="5" t="n">
+        <v>0.015548</v>
+      </c>
+      <c r="H262" s="5" t="n">
+        <v>0.023075</v>
+      </c>
+      <c r="I262" s="5" t="n">
+        <v>0.011562</v>
+      </c>
+      <c r="J262" s="5" t="n">
+        <v>0.01854</v>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>0.007669</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>0.00447</v>
+      </c>
+      <c r="M262" s="5" t="n">
+        <v>0.003806</v>
+      </c>
+      <c r="N262" s="5" t="n">
+        <v>0.024312</v>
+      </c>
+      <c r="O262" s="5" t="n">
+        <v>0.007492</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Other income – flow-through</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="5" t="n">
+        <v>0.015546</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" s="5" t="n">
+        <v>-0.012093</v>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>-1.712193</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>-1.959236</v>
+      </c>
+      <c r="M264" s="5" t="n">
+        <v>-6.330593</v>
+      </c>
+      <c r="N264" s="5" t="n">
+        <v>-2.426914</v>
+      </c>
+      <c r="O264" s="5" t="n">
+        <v>-0.035472</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Impairment of asset held for sale (Note 3)</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="5" t="n">
+        <v>-1.56947</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Part XII.6 flow through tax</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="5" t="n">
+        <v>-0.006426</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Proceeds on sale of resource property (Note 6(c))</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Realized gain on marketable securities (Note 4)</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O268" s="5" t="n">
+        <v>0.57563</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Unrealized gain on marketable securities (Note 4)</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="5" t="n">
+        <v>0.028598</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F270" s="5" t="n">
+        <v>-2.115436</v>
+      </c>
+      <c r="G270" s="5" t="n">
+        <v>-0.965961</v>
+      </c>
+      <c r="H270" s="5" t="n">
+        <v>-1.262965</v>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>-1.596192</v>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>-0.806926</v>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>-2.61256</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>-2.400945</v>
+      </c>
+      <c r="M270" s="5" t="n">
+        <v>-7.085113</v>
+      </c>
+      <c r="N270" s="5" t="n">
+        <v>-5.011613</v>
+      </c>
+      <c r="O270" s="5" t="n">
+        <v>-0.9757479999999999</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Translation adjustment</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J271" s="5" t="n">
+        <v>-0.511493</v>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>-0.032515</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>0.5016389999999999</v>
+      </c>
+      <c r="M271" s="5" t="n">
+        <v>0.022187</v>
+      </c>
+      <c r="N271" s="5" t="n">
+        <v>0.14693</v>
+      </c>
+      <c r="O271" s="5" t="n">
+        <v>-0.05701</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J272" s="5" t="n">
+        <v>-1.318419</v>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>-2.645075</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>-1.899306</v>
+      </c>
+      <c r="M272" s="5" t="n">
+        <v>-7.062926</v>
+      </c>
+      <c r="N272" s="5" t="n">
+        <v>-4.864683</v>
+      </c>
+      <c r="O272" s="5" t="n">
+        <v>-1.032758</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Loss per common share</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>-Basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F273" s="5" t="n">
+        <v>-1.3e-07</v>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J273" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="M273" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="N273" s="5" t="n">
+        <v>-4e-07</v>
+      </c>
+      <c r="O273" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>-Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F274" s="5" t="n">
+        <v>16.737212</v>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>36.092157</v>
+      </c>
+      <c r="H274" s="5" t="n">
+        <v>47.155675</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>55.859491</v>
+      </c>
+      <c r="J274" s="5" t="n">
+        <v>70.309409</v>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>81.126475</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>91.04077599999999</v>
+      </c>
+      <c r="M274" s="5" t="n">
+        <v>112.559691</v>
+      </c>
+      <c r="N274" s="5" t="n">
+        <v>12.396226</v>
+      </c>
+      <c r="O274" s="5" t="n">
+        <v>17.486256</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 12) $</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M275" s="5" t="n">
+        <v>0.07373</v>
+      </c>
+      <c r="N275" s="5" t="n">
+        <v>0.073628</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Depreciation (Note 6)</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F276" s="5" t="n">
+        <v>0.00051</v>
+      </c>
+      <c r="G276" s="5" t="n">
+        <v>0.001673</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" s="5" t="n">
+        <v>0.000475</v>
+      </c>
+      <c r="N276" s="5" t="n">
+        <v>0.00111</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Salaries (Note 12)</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" s="5" t="n">
+        <v>0.287225</v>
+      </c>
+      <c r="N277" s="5" t="n">
+        <v>0.326578</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 10 and 12)</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" s="5" t="n">
+        <v>0.242438</v>
+      </c>
+      <c r="N278" s="5" t="n">
+        <v>0.288381</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Other income – flow-through (Note 10)</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" s="5" t="n">
+        <v>0.174648</v>
+      </c>
+      <c r="N279" s="5" t="n">
+        <v>0.015546</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets (Note 7)</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" s="5" t="n">
+        <v>-6.330593</v>
+      </c>
+      <c r="N280" s="5" t="n">
+        <v>-2.426914</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Impairment of asset held for sale (Note 4)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="5" t="n">
+        <v>-1.56947</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Proceeds on sale of resource property (Note 7(d))</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Depreciation (Note 5)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H283" s="5" t="n">
+        <v>0.002237</v>
+      </c>
+      <c r="I283" s="5" t="n">
+        <v>0.00198</v>
+      </c>
+      <c r="J283" s="5" t="n">
+        <v>0.001386</v>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>0.0009700000000000001</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>0.000679</v>
+      </c>
+      <c r="M283" s="5" t="n">
+        <v>0.000475</v>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Other income – flow-through (Note 9)</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>0.123322</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>0.418758</v>
+      </c>
+      <c r="M284" s="5" t="n">
+        <v>0.174648</v>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 9(b) and 11)</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J285" s="5" t="n">
+        <v>0.216867</v>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>0.426574</v>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F286" s="5" t="n">
+        <v>0.019341</v>
+      </c>
+      <c r="G286" s="5" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="H286" s="5" t="n">
+        <v>0.022424</v>
+      </c>
+      <c r="I286" s="5" t="n">
+        <v>0.015328</v>
+      </c>
+      <c r="J286" s="5" t="n">
+        <v>0.000194</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Other income – flow-through (Note 9(a))</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>0.123322</v>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H288" s="5" t="n">
+        <v>0.08519699999999999</v>
+      </c>
+      <c r="I288" s="5" t="n">
+        <v>0.069815</v>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H289" s="5" t="n">
+        <v>-0.08019</v>
+      </c>
+      <c r="I289" s="5" t="n">
+        <v>-0.031979</v>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets (Note 6)</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H290" s="5" t="n">
+        <v>0.06461</v>
+      </c>
+      <c r="I290" s="5" t="n">
+        <v>0.885907</v>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Salaries (Note 10)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H291" s="5" t="n">
+        <v>0.375609</v>
+      </c>
+      <c r="I291" s="5" t="n">
+        <v>0.239886</v>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note 8(b) and 10)</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H292" s="5" t="n">
+        <v>0.442397</v>
+      </c>
+      <c r="I292" s="5" t="n">
+        <v>0.352186</v>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Other income – flow-through (Note 8(a))</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I293" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Translation adjustment</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F294" s="5" t="n">
+        <v>0.013139</v>
+      </c>
+      <c r="G294" s="5" t="n">
+        <v>-0.01275</v>
+      </c>
+      <c r="H294" s="5" t="n">
+        <v>0.123584</v>
+      </c>
+      <c r="I294" s="5" t="n">
+        <v>0.247218</v>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F295" s="5" t="n">
+        <v>-2.102297</v>
+      </c>
+      <c r="G295" s="5" t="n">
+        <v>-0.978711</v>
+      </c>
+      <c r="H295" s="5" t="n">
+        <v>-1.139381</v>
+      </c>
+      <c r="I295" s="5" t="n">
+        <v>-1.348974</v>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr"/>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>FOR THE YEARS ENDED MARCH</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H296" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Consulting fees (Note 10) $ 85,197 $</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H297" s="5" t="n">
+        <v>0.06378</v>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Depreciation (Note 5) 2,237</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H298" s="5" t="n">
+        <v>0.001673</v>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss (gain) (80,190)</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H299" s="5" t="n">
+        <v>0.036356</v>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Investor relations and promotion 187,218</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H300" s="5" t="n">
+        <v>0.140517</v>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets (Note 6) 64,610</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" s="5" t="n">
+        <v>0.007594</v>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Office 45,087</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" s="5" t="n">
+        <v>0.032497</v>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Professional fees 70,399</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" s="5" t="n">
+        <v>0.09639499999999999</v>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Rent 43,327</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H304" s="5" t="n">
+        <v>0.024122</v>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Salaries (Note 10) 375,609</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H305" s="5" t="n">
+        <v>0.382843</v>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note 8(b)) 442,397</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" s="5" t="n">
+        <v>0.116933</v>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Regulatory and transfer agent 27,725</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" s="5" t="n">
+        <v>0.062809</v>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Travel 22,424</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" s="5" t="n">
+        <v>0.01599</v>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Interest income 23,075</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" s="5" t="n">
+        <v>0.015548</v>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Loss for the year (1,262,965)</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" s="5" t="n">
+        <v>-0.965961</v>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Translation adjustment 123,584</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" s="5" t="n">
+        <v>-0.01275</v>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>years</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive loss for the year $ (1,139,381) $</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" s="5" t="n">
+        <v>-0.978711</v>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Loss per common share</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>-Basic and diluted $ (0.02) $</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>-Basic and diluted 47,155,675</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H314" s="5" t="n">
+        <v>36.092157</v>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F315" s="5" t="n">
+        <v>0.015308</v>
+      </c>
+      <c r="G315" s="5" t="n">
+        <v>0.036356</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Impairment of exploration and evaluation assets (Note 7(a))</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F316" s="5" t="n">
+        <v>0.026379</v>
+      </c>
+      <c r="G316" s="5" t="n">
+        <v>0.007594</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Property investigation</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F317" s="5" t="n">
+        <v>0.005399</v>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note 9(b))</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F318" s="5" t="n">
+        <v>0.540959</v>
+      </c>
+      <c r="G318" s="5" t="n">
+        <v>0.116933</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>OTHER</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
         <is>
           <t>Listing expense (Note 3)</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F250" s="5" t="n">
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F319" s="5" t="n">
         <v>-1.184674</v>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
         <is>
           <t>-</t>
         </is>
